--- a/Baltic_Sea_Multi K-means/Gadus morhua_mkm/output_sd/Baltic_Sea_2020_mkm_31_gadus_morhua_REFINEMENT.xlsx
+++ b/Baltic_Sea_Multi K-means/Gadus morhua_mkm/output_sd/Baltic_Sea_2020_mkm_31_gadus_morhua_REFINEMENT.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laura\Documents\Risk Assessment Mar Baltico - NOVEMBRE\Risk assessment_novembre\BalticEcosystemRiskAssessment\Baltico_Multi K-means\Gadus morhua\output_sd\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laura\Documents\Risk Assessment Mar Baltico - NOVEMBRE\Risk assessment_novembre\BalticEcosystemRiskAssessment\Baltic_Sea_Multi K-means\Gadus morhua_mkm\output_sd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC018A0-25CC-49B3-AA33-882219F611B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5201F285-B5C2-4734-8A6B-F5C2B73248E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35950" yWindow="100" windowWidth="32480" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38200" yWindow="100" windowWidth="38200" windowHeight="9790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all_centroidi_annotated_31_2020" sheetId="1" r:id="rId1"/>
@@ -38,187 +38,187 @@
     <t>centroid_id</t>
   </si>
   <si>
+    <t>cod_cpue_2020_std_label</t>
+  </si>
+  <si>
+    <t>bathymetry_2020_std</t>
+  </si>
+  <si>
+    <t>bathymetry_2020_std_sd</t>
+  </si>
+  <si>
+    <t>bathymetry_2020_std_label</t>
+  </si>
+  <si>
+    <t>bottom_temperature_2020_std</t>
+  </si>
+  <si>
+    <t>bottom_temperature_2020_std_sd</t>
+  </si>
+  <si>
+    <t>bottom_temperature_2020_std_label</t>
+  </si>
+  <si>
+    <t>surface_net_primary_production_2020_std</t>
+  </si>
+  <si>
+    <t>surface_net_primary_production_2020_std_sd</t>
+  </si>
+  <si>
+    <t>surface_net_primary_production_2020_std_label</t>
+  </si>
+  <si>
+    <t>fishing_activity_hours_2020_std</t>
+  </si>
+  <si>
+    <t>fishing_activity_hours_2020_std_sd</t>
+  </si>
+  <si>
+    <t>fishing_activity_hours_2020_std_label</t>
+  </si>
+  <si>
+    <t>ship_density_route_2020_std</t>
+  </si>
+  <si>
+    <t>ship_density_route_2020_std_sd</t>
+  </si>
+  <si>
+    <t>ship_density_route_2020_std_label</t>
+  </si>
+  <si>
+    <t>bottom_salinity_2020_std</t>
+  </si>
+  <si>
+    <t>bottom_salinity_2020_std_sd</t>
+  </si>
+  <si>
+    <t>bottom_salinity_2020_std_label</t>
+  </si>
+  <si>
+    <t>bottom_dissolved_oxygen_2020_inv_std</t>
+  </si>
+  <si>
+    <t>bottom_dissolved_oxygen_2020_inv_std_sd</t>
+  </si>
+  <si>
+    <t>bottom_dissolved_oxygen_2020_inv_std_label</t>
+  </si>
+  <si>
+    <t>dumping_site_2020</t>
+  </si>
+  <si>
+    <t>dumping_site_2020_sd</t>
+  </si>
+  <si>
+    <t>dumping_site_2020_label</t>
+  </si>
+  <si>
+    <t>military_area_2020</t>
+  </si>
+  <si>
+    <t>military_area_2020_sd</t>
+  </si>
+  <si>
+    <t>military_area_2020_label</t>
+  </si>
+  <si>
+    <t>wind_farm_2020</t>
+  </si>
+  <si>
+    <t>wind_farm_2020_sd</t>
+  </si>
+  <si>
+    <t>wind_farm_2020_label</t>
+  </si>
+  <si>
+    <t>bedrock_seabed_2020</t>
+  </si>
+  <si>
+    <t>bedrock_seabed_2020_sd</t>
+  </si>
+  <si>
+    <t>bedrock_seabed_2020_label</t>
+  </si>
+  <si>
+    <t>hard_bottom_seabed_2020</t>
+  </si>
+  <si>
+    <t>hard_bottom_seabed_2020_sd</t>
+  </si>
+  <si>
+    <t>hard_bottom_seabed_2020_label</t>
+  </si>
+  <si>
+    <t>attention_level</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>high attention</t>
+  </si>
+  <si>
+    <t>IF Centroid &gt;= Centroid_mean+ (SD_mean/2) --&gt; 1 o 0.5</t>
+  </si>
+  <si>
+    <t>MAIUSCOLO/minuscolo/0</t>
+  </si>
+  <si>
+    <t>BIODIVERSITY</t>
+  </si>
+  <si>
+    <t>BATHYMETRY</t>
+  </si>
+  <si>
+    <t>TEMPERATURE</t>
+  </si>
+  <si>
+    <t>NPP</t>
+  </si>
+  <si>
+    <t>FISHING</t>
+  </si>
+  <si>
+    <t>SHIP</t>
+  </si>
+  <si>
+    <t>SALINITY</t>
+  </si>
+  <si>
+    <t>OXYGEN</t>
+  </si>
+  <si>
+    <t>DUPING_SITE</t>
+  </si>
+  <si>
+    <t>MILITARY</t>
+  </si>
+  <si>
+    <t>wind_farm</t>
+  </si>
+  <si>
+    <t>WIND_FARM</t>
+  </si>
+  <si>
+    <t>BEDROCK</t>
+  </si>
+  <si>
+    <t>HARDROCK</t>
+  </si>
+  <si>
+    <t>hardrock</t>
+  </si>
+  <si>
     <t>cod_cpue_2020_std</t>
   </si>
   <si>
     <t>cod_cpue_2020_std_sd</t>
-  </si>
-  <si>
-    <t>cod_cpue_2020_std_label</t>
-  </si>
-  <si>
-    <t>bathymetry_2020_std</t>
-  </si>
-  <si>
-    <t>bathymetry_2020_std_sd</t>
-  </si>
-  <si>
-    <t>bathymetry_2020_std_label</t>
-  </si>
-  <si>
-    <t>bottom_temperature_2020_std</t>
-  </si>
-  <si>
-    <t>bottom_temperature_2020_std_sd</t>
-  </si>
-  <si>
-    <t>bottom_temperature_2020_std_label</t>
-  </si>
-  <si>
-    <t>surface_net_primary_production_2020_std</t>
-  </si>
-  <si>
-    <t>surface_net_primary_production_2020_std_sd</t>
-  </si>
-  <si>
-    <t>surface_net_primary_production_2020_std_label</t>
-  </si>
-  <si>
-    <t>fishing_activity_hours_2020_std</t>
-  </si>
-  <si>
-    <t>fishing_activity_hours_2020_std_sd</t>
-  </si>
-  <si>
-    <t>fishing_activity_hours_2020_std_label</t>
-  </si>
-  <si>
-    <t>ship_density_route_2020_std</t>
-  </si>
-  <si>
-    <t>ship_density_route_2020_std_sd</t>
-  </si>
-  <si>
-    <t>ship_density_route_2020_std_label</t>
-  </si>
-  <si>
-    <t>bottom_salinity_2020_std</t>
-  </si>
-  <si>
-    <t>bottom_salinity_2020_std_sd</t>
-  </si>
-  <si>
-    <t>bottom_salinity_2020_std_label</t>
-  </si>
-  <si>
-    <t>bottom_dissolved_oxygen_2020_inv_std</t>
-  </si>
-  <si>
-    <t>bottom_dissolved_oxygen_2020_inv_std_sd</t>
-  </si>
-  <si>
-    <t>bottom_dissolved_oxygen_2020_inv_std_label</t>
-  </si>
-  <si>
-    <t>dumping_site_2020</t>
-  </si>
-  <si>
-    <t>dumping_site_2020_sd</t>
-  </si>
-  <si>
-    <t>dumping_site_2020_label</t>
-  </si>
-  <si>
-    <t>military_area_2020</t>
-  </si>
-  <si>
-    <t>military_area_2020_sd</t>
-  </si>
-  <si>
-    <t>military_area_2020_label</t>
-  </si>
-  <si>
-    <t>wind_farm_2020</t>
-  </si>
-  <si>
-    <t>wind_farm_2020_sd</t>
-  </si>
-  <si>
-    <t>wind_farm_2020_label</t>
-  </si>
-  <si>
-    <t>bedrock_seabed_2020</t>
-  </si>
-  <si>
-    <t>bedrock_seabed_2020_sd</t>
-  </si>
-  <si>
-    <t>bedrock_seabed_2020_label</t>
-  </si>
-  <si>
-    <t>hard_bottom_seabed_2020</t>
-  </si>
-  <si>
-    <t>hard_bottom_seabed_2020_sd</t>
-  </si>
-  <si>
-    <t>hard_bottom_seabed_2020_label</t>
-  </si>
-  <si>
-    <t>attention_level</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>high attention</t>
-  </si>
-  <si>
-    <t>IF Centroid &gt;= Centroid_mean+ (SD_mean/2) --&gt; 1 o 0.5</t>
-  </si>
-  <si>
-    <t>MAIUSCOLO/minuscolo/0</t>
-  </si>
-  <si>
-    <t>BIODIVERSITY</t>
-  </si>
-  <si>
-    <t>BATHYMETRY</t>
-  </si>
-  <si>
-    <t>TEMPERATURE</t>
-  </si>
-  <si>
-    <t>NPP</t>
-  </si>
-  <si>
-    <t>FISHING</t>
-  </si>
-  <si>
-    <t>SHIP</t>
-  </si>
-  <si>
-    <t>SALINITY</t>
-  </si>
-  <si>
-    <t>OXYGEN</t>
-  </si>
-  <si>
-    <t>DUPING_SITE</t>
-  </si>
-  <si>
-    <t>MILITARY</t>
-  </si>
-  <si>
-    <t>wind_farm</t>
-  </si>
-  <si>
-    <t>WIND_FARM</t>
-  </si>
-  <si>
-    <t>BEDROCK</t>
-  </si>
-  <si>
-    <t>HARDROCK</t>
-  </si>
-  <si>
-    <t>hardrock</t>
   </si>
 </sst>
 </file>
@@ -1253,202 +1253,202 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="X1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AA1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AB1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AF1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AC1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AG1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AK1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AH1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AL1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AP1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AU1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AR1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AV1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AX1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AW1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AY1" s="4" t="s">
+      <c r="BA1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AZ1" s="5" t="s">
+      <c r="BB1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="BD1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="BA1" s="5" t="s">
+      <c r="BE1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="BB1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BC1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="BD1" s="5" t="s">
+      <c r="BF1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BE1" s="4" t="s">
+      <c r="BG1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="BH1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BF1" s="4" t="s">
+      <c r="BJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="BG1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="BI1" s="4" t="s">
+      <c r="BK1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="BJ1" s="5" t="s">
+      <c r="BL1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="BM1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="BN1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="BK1" s="5" t="s">
+      <c r="BO1" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="BL1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BM1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="BN1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="BO1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G2" s="4">
         <v>0.94892571317378704</v>
@@ -1480,10 +1480,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L2" s="5">
         <v>-0.91765231801309499</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="4">
         <v>0.30652561582078902</v>
@@ -1510,10 +1510,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V2" s="5">
         <v>3.4755566745998001</v>
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA2" s="4">
         <v>-0.16267436559766699</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AD2" s="9"/>
       <c r="AE2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF2" s="5">
         <v>-0.481841765447935</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AI2" s="8"/>
       <c r="AJ2" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK2" s="4">
         <v>0.39321757268658097</v>
@@ -1570,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="AN2" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AP2" s="5">
         <v>8.8235294117647106E-2</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AS2" s="8"/>
       <c r="AT2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU2" s="4">
         <v>0.14705882352941199</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AX2" s="9"/>
       <c r="AY2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ2" s="5">
         <v>0</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BC2" s="8"/>
       <c r="BD2" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BE2" s="4">
         <v>0</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="BH2" s="9"/>
       <c r="BI2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ2" s="5">
         <v>0</v>
@@ -1643,10 +1643,10 @@
       </c>
       <c r="BM2" s="8"/>
       <c r="BN2" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4">
         <v>-0.82562057535048305</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L3" s="5">
         <v>0.57126179520430098</v>
@@ -1694,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q3" s="4">
         <v>0.52014367488506896</v>
@@ -1710,10 +1710,10 @@
         <v>1</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V3" s="5">
         <v>-0.30021581067063202</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y3" s="8"/>
       <c r="Z3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AA3" s="4">
         <v>-0.13503925848588499</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AD3" s="9"/>
       <c r="AE3" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF3" s="5">
         <v>-0.34998693706862199</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AI3" s="8"/>
       <c r="AJ3" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK3" s="4">
         <v>-0.68330249056594505</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AN3" s="9"/>
       <c r="AO3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP3" s="5">
         <v>0</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AS3" s="8"/>
       <c r="AT3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AU3" s="4">
         <v>0</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AX3" s="9"/>
       <c r="AY3" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AZ3" s="5">
         <v>0.04</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="BC3" s="8"/>
       <c r="BD3" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE3" s="4">
         <v>0.04</v>
@@ -1824,10 +1824,10 @@
         <v>1</v>
       </c>
       <c r="BH3" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="BI3" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BJ3" s="5">
         <v>0.16</v>
@@ -1840,13 +1840,13 @@
         <v>0.5</v>
       </c>
       <c r="BM3" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="BN3" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4">
         <v>1.20723832601296</v>
@@ -1878,10 +1878,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L4" s="5">
         <v>-0.18636304276499599</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="O4" s="8"/>
       <c r="P4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="4">
         <v>-0.265224306333606</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="T4" s="9"/>
       <c r="U4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V4" s="5">
         <v>0.30112723547397802</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA4" s="4">
         <v>-0.16109691829834699</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AD4" s="9"/>
       <c r="AE4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF4" s="5">
         <v>0.123403999914382</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AK4" s="4">
         <v>1.11112053264503</v>
@@ -1964,10 +1964,10 @@
         <v>1</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AO4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AP4" s="5">
         <v>0.86792452830188704</v>
@@ -1980,10 +1980,10 @@
         <v>1</v>
       </c>
       <c r="AS4" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AT4" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU4" s="4">
         <v>0.55660377358490598</v>
@@ -1996,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="AX4" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AY4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ4" s="5">
         <v>5.6603773584905703E-2</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="BC4" s="8"/>
       <c r="BD4" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE4" s="4">
         <v>0</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="BH4" s="9"/>
       <c r="BI4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ4" s="5">
         <v>9.4339622641509396E-3</v>
@@ -2041,10 +2041,10 @@
       </c>
       <c r="BM4" s="8"/>
       <c r="BN4" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5" s="4">
         <v>-1.0318967003125299</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L5" s="5">
         <v>1.23980016960318</v>
@@ -2090,10 +2090,10 @@
         <v>1</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="4">
         <v>0.106232262495299</v>
@@ -2106,10 +2106,10 @@
         <v>1</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V5" s="5">
         <v>-0.45006063207057601</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="Y5" s="8"/>
       <c r="Z5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA5" s="4">
         <v>-0.283775682717338</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AD5" s="9"/>
       <c r="AE5" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF5" s="5">
         <v>-0.273571654006041</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AK5" s="4">
         <v>-0.73882648087360803</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AN5" s="9"/>
       <c r="AO5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP5" s="5">
         <v>6.4102564102564097E-2</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AS5" s="8"/>
       <c r="AT5" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU5" s="4">
         <v>1.2820512820512799E-2</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AX5" s="9"/>
       <c r="AY5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ5" s="5">
         <v>8.9743589743589702E-2</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="BC5" s="8"/>
       <c r="BD5" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE5" s="4">
         <v>3.8461538461538498E-2</v>
@@ -2220,10 +2220,10 @@
         <v>1</v>
       </c>
       <c r="BH5" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="BI5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BJ5" s="5">
         <v>0</v>
@@ -2237,10 +2237,10 @@
       </c>
       <c r="BM5" s="8"/>
       <c r="BN5" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BO5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="4">
         <v>-0.35445874940983002</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L6" s="5">
         <v>0.67910744984222904</v>
@@ -2286,10 +2286,10 @@
         <v>1</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q6" s="4">
         <v>-0.38470738137951099</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="T6" s="9"/>
       <c r="U6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V6" s="5">
         <v>1.8836617692405</v>
@@ -2316,10 +2316,10 @@
         <v>1</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA6" s="4">
         <v>2.48403579660854E-2</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AD6" s="9"/>
       <c r="AE6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF6" s="5">
         <v>2.3228342319337201</v>
@@ -2346,10 +2346,10 @@
         <v>1</v>
       </c>
       <c r="AI6" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AJ6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK6" s="4">
         <v>-0.290018024789988</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AN6" s="9"/>
       <c r="AO6" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AP6" s="5">
         <v>0</v>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AS6" s="8"/>
       <c r="AT6" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AU6" s="4">
         <v>2.6315789473684199E-2</v>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AX6" s="9"/>
       <c r="AY6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ6" s="5">
         <v>0.157894736842105</v>
@@ -2404,10 +2404,10 @@
         <v>0.5</v>
       </c>
       <c r="BC6" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BD6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE6" s="4">
         <v>0</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="BH6" s="9"/>
       <c r="BI6" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ6" s="5">
         <v>0.105263157894737</v>
@@ -2435,10 +2435,10 @@
       </c>
       <c r="BM6" s="8"/>
       <c r="BN6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4">
         <v>0.28114737115667798</v>
@@ -2470,10 +2470,10 @@
         <v>1</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L7" s="5">
         <v>-0.31732128905349699</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="4">
         <v>-0.179877838760337</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="T7" s="9"/>
       <c r="U7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V7" s="5">
         <v>1.43164120378608</v>
@@ -2514,10 +2514,10 @@
         <v>1</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA7" s="4">
         <v>-0.23043115213021401</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AD7" s="9"/>
       <c r="AE7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF7" s="5">
         <v>-0.43888944683458597</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK7" s="4">
         <v>-6.9254151626540403E-2</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AN7" s="9"/>
       <c r="AO7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AP7" s="5">
         <v>0.11267605633802801</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AS7" s="8"/>
       <c r="AT7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU7" s="4">
         <v>8.4507042253521097E-2</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AX7" s="9"/>
       <c r="AY7" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ7" s="5">
         <v>0.140845070422535</v>
@@ -2600,10 +2600,10 @@
         <v>0.5</v>
       </c>
       <c r="BC7" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BD7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE7" s="4">
         <v>0</v>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="BH7" s="9"/>
       <c r="BI7" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ7" s="5">
         <v>5.63380281690141E-2</v>
@@ -2631,10 +2631,10 @@
       </c>
       <c r="BM7" s="8"/>
       <c r="BN7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -2652,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <v>0.75084486959653496</v>
@@ -2668,10 +2668,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L8" s="5">
         <v>-0.77024428464247796</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="4">
         <v>-0.17331463872885999</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="T8" s="9"/>
       <c r="U8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V8" s="5">
         <v>1.6656041655501701E-2</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y8" s="8"/>
       <c r="Z8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA8" s="4">
         <v>-0.22897037007819701</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="AD8" s="9"/>
       <c r="AE8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF8" s="5">
         <v>-0.37221641685219597</v>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AI8" s="8"/>
       <c r="AJ8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK8" s="4">
         <v>0.20138674479324001</v>
@@ -2754,10 +2754,10 @@
         <v>1</v>
       </c>
       <c r="AN8" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AO8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AP8" s="5">
         <v>9.0909090909090898E-2</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AS8" s="8"/>
       <c r="AT8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU8" s="4">
         <v>6.0606060606060601E-2</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX8" s="9"/>
       <c r="AY8" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ8" s="5">
         <v>0</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="BC8" s="8"/>
       <c r="BD8" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BE8" s="4">
         <v>0</v>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="BH8" s="9"/>
       <c r="BI8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ8" s="5">
         <v>0.15151515151515199</v>
@@ -2826,13 +2826,13 @@
         <v>0.5</v>
       </c>
       <c r="BM8" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="BN8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO8" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="4">
         <v>-0.52058012090184902</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L9" s="5">
         <v>0.915831861748308</v>
@@ -2878,10 +2878,10 @@
         <v>1</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q9" s="4">
         <v>-4.7542159487341598E-2</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="T9" s="9"/>
       <c r="U9" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V9" s="5">
         <v>-0.31173719741275902</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Y9" s="8"/>
       <c r="Z9" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AA9" s="4">
         <v>1.1858748781762001</v>
@@ -2922,10 +2922,10 @@
         <v>1</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF9" s="5">
         <v>-7.6493639945777805E-2</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AK9" s="4">
         <v>-0.515906175946795</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="AN9" s="9"/>
       <c r="AO9" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP9" s="5">
         <v>2.0833333333333301E-2</v>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AS9" s="8"/>
       <c r="AT9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU9" s="4">
         <v>0.25</v>
@@ -2980,10 +2980,10 @@
         <v>1</v>
       </c>
       <c r="AX9" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AY9" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ9" s="5">
         <v>8.3333333333333301E-2</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="BC9" s="8"/>
       <c r="BD9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE9" s="4">
         <v>0</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="BH9" s="9"/>
       <c r="BI9" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ9" s="5">
         <v>8.3333333333333301E-2</v>
@@ -3025,10 +3025,10 @@
       </c>
       <c r="BM9" s="8"/>
       <c r="BN9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="4">
         <v>-5.5321782640842997E-2</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L10" s="5">
         <v>0.49641766388690201</v>
@@ -3074,10 +3074,10 @@
         <v>1</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="4">
         <v>-0.40278157774777101</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="T10" s="9"/>
       <c r="U10" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V10" s="5">
         <v>3.8335656191602001</v>
@@ -3104,10 +3104,10 @@
         <v>1</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA10" s="4">
         <v>0.59925838090439099</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AD10" s="9"/>
       <c r="AE10" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF10" s="5">
         <v>2.4234810771396198</v>
@@ -3134,10 +3134,10 @@
         <v>1</v>
       </c>
       <c r="AI10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AJ10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK10" s="4">
         <v>-0.243912633230463</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AN10" s="9"/>
       <c r="AO10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AP10" s="5">
         <v>0</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="AS10" s="8"/>
       <c r="AT10" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AU10" s="4">
         <v>2.2222222222222199E-2</v>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="AX10" s="9"/>
       <c r="AY10" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ10" s="5">
         <v>0.24444444444444399</v>
@@ -3192,10 +3192,10 @@
         <v>1</v>
       </c>
       <c r="BC10" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="BD10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BE10" s="4">
         <v>0</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="BH10" s="9"/>
       <c r="BI10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ10" s="5">
         <v>0.11111111111111099</v>
@@ -3223,10 +3223,10 @@
       </c>
       <c r="BM10" s="8"/>
       <c r="BN10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4">
         <v>-0.56324509781799803</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L11" s="5">
         <v>0.95102558464158304</v>
@@ -3272,10 +3272,10 @@
         <v>1</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q11" s="4">
         <v>-0.14921463528833401</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="T11" s="9"/>
       <c r="U11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V11" s="5">
         <v>-8.1870026972179297E-3</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA11" s="4">
         <v>6.1148485418142098</v>
@@ -3316,10 +3316,10 @@
         <v>1</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF11" s="5">
         <v>0.938466649822295</v>
@@ -3332,10 +3332,10 @@
         <v>1</v>
       </c>
       <c r="AI11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AJ11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK11" s="4">
         <v>-0.35051713666388501</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AN11" s="9"/>
       <c r="AO11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AP11" s="5">
         <v>4.1666666666666699E-2</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AS11" s="8"/>
       <c r="AT11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AU11" s="4">
         <v>0.16666666666666699</v>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="AX11" s="9"/>
       <c r="AY11" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ11" s="5">
         <v>0</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BC11" s="8"/>
       <c r="BD11" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BE11" s="4">
         <v>0</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="BH11" s="9"/>
       <c r="BI11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="BJ11" s="5">
         <v>0.25</v>
@@ -3418,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="BM11" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="BN11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BO11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:67" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -3634,19 +3634,19 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="16"/>
       <c r="I16" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J16" s="16"/>
       <c r="K16" s="15"/>
@@ -3662,41 +3662,41 @@
         <v>2</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M17" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="18" t="s">
         <v>59</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>61</v>
       </c>
       <c r="O17" s="19">
         <v>4.5</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="15"/>
@@ -3719,13 +3719,13 @@
       <c r="G18" s="15"/>
       <c r="H18" s="16"/>
       <c r="I18" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="15" t="s">
         <v>54</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>56</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="15"/>
@@ -3741,10 +3741,10 @@
       <c r="B19" s="14"/>
       <c r="C19" s="15"/>
       <c r="D19" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="15"/>
@@ -3754,7 +3754,7 @@
       <c r="K19" s="15"/>
       <c r="L19" s="16"/>
       <c r="M19" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N19" s="16"/>
       <c r="O19" s="1">
@@ -3768,21 +3768,21 @@
       <c r="B20" s="14"/>
       <c r="C20" s="15"/>
       <c r="D20" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="16"/>
       <c r="K20" s="15"/>
       <c r="L20" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="16"/>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="16"/>
@@ -3809,7 +3809,7 @@
       <c r="J21" s="16"/>
       <c r="K21" s="15"/>
       <c r="L21" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="16"/>
@@ -3822,43 +3822,43 @@
         <v>21</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O22" s="19">
         <v>3.5</v>
@@ -3874,18 +3874,18 @@
       <c r="B23" s="14"/>
       <c r="C23" s="15"/>
       <c r="D23" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16"/>
       <c r="G23" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H23" s="16"/>
       <c r="I23" s="15"/>
       <c r="J23" s="16"/>
       <c r="K23" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="15"/>
@@ -3901,21 +3901,21 @@
       <c r="B24" s="14"/>
       <c r="C24" s="15"/>
       <c r="D24" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="16"/>
       <c r="K24" s="15"/>
       <c r="L24" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="16"/>
@@ -3930,15 +3930,15 @@
       <c r="B25" s="14"/>
       <c r="C25" s="15"/>
       <c r="D25" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16"/>
       <c r="G25" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="16"/>
@@ -3946,7 +3946,7 @@
       <c r="L25" s="16"/>
       <c r="M25" s="15"/>
       <c r="N25" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O25" s="1">
         <v>4</v>
@@ -3957,43 +3957,43 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -4481,43 +4481,43 @@
         <v>0</v>
       </c>
       <c r="B45" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="E45" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="F45" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="G45" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="H45" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G45" s="21" t="s">
+      <c r="I45" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="J45" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="K45" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J45" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="K45" s="21" t="s">
+      <c r="L45" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="L45" s="21" t="s">
+      <c r="M45" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="M45" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="N45" s="21" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -4525,43 +4525,43 @@
         <v>2</v>
       </c>
       <c r="B46" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>49</v>
-      </c>
       <c r="E46" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J46" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L46" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M46" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="20" t="s">
         <v>59</v>
-      </c>
-      <c r="N46" s="20" t="s">
-        <v>61</v>
       </c>
       <c r="O46" s="13">
         <v>4.5</v>
@@ -4575,43 +4575,43 @@
         <v>21</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K47" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L47" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M47" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O47" s="13">
         <v>3.5</v>
